--- a/data/nzd0603/nzd0603.xlsx
+++ b/data/nzd0603/nzd0603.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R364"/>
+  <dimension ref="A1:R366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22171,7 +22171,7 @@
         <v>219.96</v>
       </c>
       <c r="G363" t="n">
-        <v>224.2</v>
+        <v>209.29</v>
       </c>
       <c r="H363" t="n">
         <v>198.47</v>
@@ -22231,7 +22231,7 @@
         <v>214.63</v>
       </c>
       <c r="G364" t="n">
-        <v>224.2</v>
+        <v>209.29</v>
       </c>
       <c r="H364" t="n">
         <v>197.2</v>
@@ -22246,7 +22246,7 @@
         <v>245.4</v>
       </c>
       <c r="L364" t="n">
-        <v>246.39</v>
+        <v>266.49</v>
       </c>
       <c r="M364" t="n">
         <v>224.89</v>
@@ -22264,6 +22264,126 @@
         <v>223.4</v>
       </c>
       <c r="R364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>233.07</v>
+      </c>
+      <c r="C365" t="n">
+        <v>216.55</v>
+      </c>
+      <c r="D365" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="E365" t="n">
+        <v>217.38</v>
+      </c>
+      <c r="F365" t="n">
+        <v>215.71</v>
+      </c>
+      <c r="G365" t="n">
+        <v>213.01</v>
+      </c>
+      <c r="H365" t="n">
+        <v>201.13</v>
+      </c>
+      <c r="I365" t="n">
+        <v>206.71</v>
+      </c>
+      <c r="J365" t="n">
+        <v>219.14</v>
+      </c>
+      <c r="K365" t="n">
+        <v>259.52</v>
+      </c>
+      <c r="L365" t="n">
+        <v>281.35</v>
+      </c>
+      <c r="M365" t="n">
+        <v>230.31</v>
+      </c>
+      <c r="N365" t="n">
+        <v>216.04</v>
+      </c>
+      <c r="O365" t="n">
+        <v>220.47</v>
+      </c>
+      <c r="P365" t="n">
+        <v>236.24</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>235.48</v>
+      </c>
+      <c r="C366" t="n">
+        <v>218.64</v>
+      </c>
+      <c r="D366" t="n">
+        <v>227.23</v>
+      </c>
+      <c r="E366" t="n">
+        <v>219.94</v>
+      </c>
+      <c r="F366" t="n">
+        <v>215.07</v>
+      </c>
+      <c r="G366" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="H366" t="n">
+        <v>204.78</v>
+      </c>
+      <c r="I366" t="n">
+        <v>211.85</v>
+      </c>
+      <c r="J366" t="n">
+        <v>222.31</v>
+      </c>
+      <c r="K366" t="n">
+        <v>274.51</v>
+      </c>
+      <c r="L366" t="n">
+        <v>293.69</v>
+      </c>
+      <c r="M366" t="n">
+        <v>231.93</v>
+      </c>
+      <c r="N366" t="n">
+        <v>217.83</v>
+      </c>
+      <c r="O366" t="n">
+        <v>219.96</v>
+      </c>
+      <c r="P366" t="n">
+        <v>242.75</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>228.92</v>
+      </c>
+      <c r="R366" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -22280,7 +22400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B374"/>
+  <dimension ref="A1:B376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26023,6 +26143,26 @@
       </c>
       <c r="B374" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -26185,28 +26325,28 @@
         <v>0.0619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06417079775937054</v>
+        <v>0.06610337059642483</v>
       </c>
       <c r="J2" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K2" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009916497633014165</v>
+        <v>0.0106211595719965</v>
       </c>
       <c r="M2" t="n">
-        <v>3.415341198291022</v>
+        <v>3.4077251853987</v>
       </c>
       <c r="N2" t="n">
-        <v>22.49055021532211</v>
+        <v>22.39337408101193</v>
       </c>
       <c r="O2" t="n">
-        <v>4.742420290877024</v>
+        <v>4.732163784254717</v>
       </c>
       <c r="P2" t="n">
-        <v>230.7552861364067</v>
+        <v>230.7350450363648</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26257,28 +26397,28 @@
         <v>0.0871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1727135958070923</v>
+        <v>0.1654138627581607</v>
       </c>
       <c r="J3" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06088925310909699</v>
+        <v>0.05616356286532642</v>
       </c>
       <c r="M3" t="n">
-        <v>3.518188762456562</v>
+        <v>3.529210912868224</v>
       </c>
       <c r="N3" t="n">
-        <v>25.12455571453215</v>
+        <v>25.25239613410625</v>
       </c>
       <c r="O3" t="n">
-        <v>5.012440095854727</v>
+        <v>5.025176229159158</v>
       </c>
       <c r="P3" t="n">
-        <v>219.9956877321371</v>
+        <v>220.0722867987749</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26329,28 +26469,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2132705825916632</v>
+        <v>0.2054688003643537</v>
       </c>
       <c r="J4" t="n">
+        <v>365</v>
+      </c>
+      <c r="K4" t="n">
         <v>363</v>
       </c>
-      <c r="K4" t="n">
-        <v>361</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06747239040942732</v>
+        <v>0.06305565936270641</v>
       </c>
       <c r="M4" t="n">
-        <v>3.972668558450319</v>
+        <v>3.997846538988547</v>
       </c>
       <c r="N4" t="n">
-        <v>34.53818788497863</v>
+        <v>34.66000570774716</v>
       </c>
       <c r="O4" t="n">
-        <v>5.876919931816208</v>
+        <v>5.887274896566931</v>
       </c>
       <c r="P4" t="n">
-        <v>227.6143111856198</v>
+        <v>227.6957796581765</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26401,28 +26541,28 @@
         <v>0.1326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4646975908414309</v>
+        <v>0.4586225393735585</v>
       </c>
       <c r="J5" t="n">
+        <v>365</v>
+      </c>
+      <c r="K5" t="n">
         <v>363</v>
       </c>
-      <c r="K5" t="n">
-        <v>361</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2167187576357834</v>
+        <v>0.2134052353074795</v>
       </c>
       <c r="M5" t="n">
-        <v>4.538694992168395</v>
+        <v>4.548108116202442</v>
       </c>
       <c r="N5" t="n">
-        <v>42.88092060812966</v>
+        <v>42.83550683264401</v>
       </c>
       <c r="O5" t="n">
-        <v>6.548352510985467</v>
+        <v>6.54488401980081</v>
       </c>
       <c r="P5" t="n">
-        <v>212.2728844095603</v>
+        <v>212.336319132464</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26473,28 +26613,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3135993304920635</v>
+        <v>0.3141249204889434</v>
       </c>
       <c r="J6" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K6" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1155285198191714</v>
+        <v>0.1170166812579085</v>
       </c>
       <c r="M6" t="n">
-        <v>4.539580195691872</v>
+        <v>4.517089670920249</v>
       </c>
       <c r="N6" t="n">
-        <v>41.18665958774211</v>
+        <v>40.96294261139854</v>
       </c>
       <c r="O6" t="n">
-        <v>6.417683350535621</v>
+        <v>6.400229887386744</v>
       </c>
       <c r="P6" t="n">
-        <v>206.6643018931656</v>
+        <v>206.6588120420485</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26545,28 +26685,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4580037677782041</v>
+        <v>0.4358566083881402</v>
       </c>
       <c r="J7" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K7" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2920367015731379</v>
+        <v>0.2652085356923408</v>
       </c>
       <c r="M7" t="n">
-        <v>3.797119034330871</v>
+        <v>3.887013283582231</v>
       </c>
       <c r="N7" t="n">
-        <v>27.81782065964169</v>
+        <v>28.95646330123864</v>
       </c>
       <c r="O7" t="n">
-        <v>5.274260200221609</v>
+        <v>5.381121007860596</v>
       </c>
       <c r="P7" t="n">
-        <v>211.1166173734753</v>
+        <v>211.347332222951</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26617,28 +26757,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1609196111525434</v>
+        <v>0.1488672904966792</v>
       </c>
       <c r="J8" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04972192496676264</v>
+        <v>0.04222441098443652</v>
       </c>
       <c r="M8" t="n">
-        <v>3.535503619115931</v>
+        <v>3.594096454626023</v>
       </c>
       <c r="N8" t="n">
-        <v>27.13127291082373</v>
+        <v>27.71441398646087</v>
       </c>
       <c r="O8" t="n">
-        <v>5.208768847897143</v>
+        <v>5.264448117937992</v>
       </c>
       <c r="P8" t="n">
-        <v>210.2341911333077</v>
+        <v>210.3601350728319</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26689,28 +26829,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1881106318295389</v>
+        <v>0.1807173595029905</v>
       </c>
       <c r="J9" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K9" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08640273745104421</v>
+        <v>0.08000954205093358</v>
       </c>
       <c r="M9" t="n">
-        <v>3.048962281674293</v>
+        <v>3.073846188402372</v>
       </c>
       <c r="N9" t="n">
-        <v>20.46754075101308</v>
+        <v>20.65964832515063</v>
       </c>
       <c r="O9" t="n">
-        <v>4.524106624629119</v>
+        <v>4.545288585464142</v>
       </c>
       <c r="P9" t="n">
-        <v>211.4036647116016</v>
+        <v>211.4809363509155</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26761,28 +26901,28 @@
         <v>0.0697</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005403295922908137</v>
+        <v>-0.009956237753963742</v>
       </c>
       <c r="J10" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K10" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L10" t="n">
-        <v>1.200479103879992e-05</v>
+        <v>4.085550313148723e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>9.209643175621496</v>
+        <v>9.229037907255156</v>
       </c>
       <c r="N10" t="n">
-        <v>133.0360617331817</v>
+        <v>133.4762057126491</v>
       </c>
       <c r="O10" t="n">
-        <v>11.53412596312272</v>
+        <v>11.55319028288936</v>
       </c>
       <c r="P10" t="n">
-        <v>235.227329099621</v>
+        <v>235.387946201502</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26833,28 +26973,28 @@
         <v>0.0313</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3474204537923182</v>
+        <v>-0.339156481418856</v>
       </c>
       <c r="J11" t="n">
+        <v>365</v>
+      </c>
+      <c r="K11" t="n">
         <v>363</v>
       </c>
-      <c r="K11" t="n">
-        <v>361</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.03284376901369668</v>
+        <v>0.03158719426556844</v>
       </c>
       <c r="M11" t="n">
-        <v>10.34093076924624</v>
+        <v>10.34188091408395</v>
       </c>
       <c r="N11" t="n">
-        <v>195.0204248113552</v>
+        <v>194.589733932278</v>
       </c>
       <c r="O11" t="n">
-        <v>13.96497135018025</v>
+        <v>13.94954242734427</v>
       </c>
       <c r="P11" t="n">
-        <v>268.2814287480961</v>
+        <v>268.1948368592135</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26905,28 +27045,28 @@
         <v>0.0382</v>
       </c>
       <c r="I12" t="n">
-        <v>1.015394449906325</v>
+        <v>1.055204354024442</v>
       </c>
       <c r="J12" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K12" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1865758728045339</v>
+        <v>0.1977198835107682</v>
       </c>
       <c r="M12" t="n">
-        <v>11.21179813446106</v>
+        <v>11.33454946469856</v>
       </c>
       <c r="N12" t="n">
-        <v>246.5690726324698</v>
+        <v>249.2415456650735</v>
       </c>
       <c r="O12" t="n">
-        <v>15.70251803477614</v>
+        <v>15.78738565010286</v>
       </c>
       <c r="P12" t="n">
-        <v>232.9609534393238</v>
+        <v>232.5454652160234</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26977,28 +27117,28 @@
         <v>0.1141</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4499547922612325</v>
+        <v>0.4418766913363186</v>
       </c>
       <c r="J13" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K13" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08584787201239152</v>
+        <v>0.08369310679889574</v>
       </c>
       <c r="M13" t="n">
-        <v>6.233982406640767</v>
+        <v>6.243207182394217</v>
       </c>
       <c r="N13" t="n">
-        <v>117.2234377792916</v>
+        <v>116.8998044304105</v>
       </c>
       <c r="O13" t="n">
-        <v>10.82697731498924</v>
+        <v>10.81202129254334</v>
       </c>
       <c r="P13" t="n">
-        <v>226.9861634638511</v>
+        <v>227.0710406764238</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27049,28 +27189,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03146471560762804</v>
+        <v>0.03093109674258512</v>
       </c>
       <c r="J14" t="n">
+        <v>365</v>
+      </c>
+      <c r="K14" t="n">
         <v>363</v>
       </c>
-      <c r="K14" t="n">
-        <v>361</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.00149420987835136</v>
+        <v>0.001460020186228261</v>
       </c>
       <c r="M14" t="n">
-        <v>4.141638475658613</v>
+        <v>4.123631534869624</v>
       </c>
       <c r="N14" t="n">
-        <v>36.05018859187437</v>
+        <v>35.85735258642092</v>
       </c>
       <c r="O14" t="n">
-        <v>6.004180925977694</v>
+        <v>5.988100916519437</v>
       </c>
       <c r="P14" t="n">
-        <v>216.6177035647407</v>
+        <v>216.6232877384011</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27121,28 +27261,28 @@
         <v>0.1828</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.01714780181202242</v>
+        <v>-0.0231715491057289</v>
       </c>
       <c r="J15" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K15" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0002788967592485259</v>
+        <v>0.0005132617466458989</v>
       </c>
       <c r="M15" t="n">
-        <v>5.267468894412348</v>
+        <v>5.265117646099612</v>
       </c>
       <c r="N15" t="n">
-        <v>57.78322119047186</v>
+        <v>57.64415067643471</v>
       </c>
       <c r="O15" t="n">
-        <v>7.601527556384431</v>
+        <v>7.592374508441658</v>
       </c>
       <c r="P15" t="n">
-        <v>226.4039920480052</v>
+        <v>226.4669654231213</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27193,28 +27333,28 @@
         <v>0.0747</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9810847212925109</v>
+        <v>0.9697370413779861</v>
       </c>
       <c r="J16" t="n">
+        <v>365</v>
+      </c>
+      <c r="K16" t="n">
         <v>363</v>
       </c>
-      <c r="K16" t="n">
-        <v>361</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1556304575698599</v>
+        <v>0.1537348054470583</v>
       </c>
       <c r="M16" t="n">
-        <v>12.08577656328097</v>
+        <v>12.05430471538542</v>
       </c>
       <c r="N16" t="n">
-        <v>284.5587372098468</v>
+        <v>283.6764163853453</v>
       </c>
       <c r="O16" t="n">
-        <v>16.86886887760548</v>
+        <v>16.84269623265068</v>
       </c>
       <c r="P16" t="n">
-        <v>224.5451321856375</v>
+        <v>224.6642448742422</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27265,28 +27405,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3813411082773954</v>
+        <v>0.3744141585757032</v>
       </c>
       <c r="J17" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K17" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L17" t="n">
-        <v>0.114333835428309</v>
+        <v>0.1113970648036677</v>
       </c>
       <c r="M17" t="n">
-        <v>5.633373842782594</v>
+        <v>5.623592905340803</v>
       </c>
       <c r="N17" t="n">
-        <v>61.62177754404866</v>
+        <v>61.52054354226006</v>
       </c>
       <c r="O17" t="n">
-        <v>7.849953983562494</v>
+        <v>7.843503269729672</v>
       </c>
       <c r="P17" t="n">
-        <v>224.9824254978617</v>
+        <v>225.0548661060871</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27324,7 +27464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R364"/>
+  <dimension ref="A1:R366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60596,7 +60736,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>-36.94966126156299,175.15555861085312</t>
+          <t>-36.94978459499662,175.15549224130928</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -60688,7 +60828,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>-36.94966126156299,175.15555861085312</t>
+          <t>-36.94978459499662,175.15549224130928</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -60713,7 +60853,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>-36.95030689184841,175.15979168900407</t>
+          <t>-36.950126375090285,175.15980992315795</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -60742,6 +60882,190 @@
         </is>
       </c>
       <c r="R364" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>-36.947506759863984,175.15215275479568</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>-36.94812828053242,175.1526440538258</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>-36.94854024555872,175.15330431696793</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-36.94897599284224,175.1540241601609</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>-36.94937166916708,175.15477513307079</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>-36.94975382368022,175.15550880032944</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>-36.95013791187851,175.15628042259823</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>-36.95037756871579,175.15712977505572</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>-36.950434881334935,175.15797661859867</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>-36.950130605095964,175.1589084263964</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>-36.949992918419014,175.15982340368967</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>-36.950509665651396,175.16067227951913</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>-36.95045277121628,175.16146135695183</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>-36.95021950047125,175.16231259449754</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>-36.94974181542913,175.16288803323746</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>-36.949385838774,175.16367435829298</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-36.94749165706835,175.15217219468636</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-36.94811518301718,175.15266091253073</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-36.94851779364038,175.15332183390842</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-36.94895645074383,175.1540394287254</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-36.949376554321816,175.15477131517935</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-36.94969186744829,175.15554214089838</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-36.95010772076039,175.1562966734294</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-36.95033505285438,175.1571526593687</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-36.950406411855106,175.15797949587238</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-36.94999598095555,175.1589220264534</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-36.94988209369795,175.15983459812847</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-36.95049511653457,175.1606737489737</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-36.950437243964664,175.16145592076973</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-36.950223924424336,175.16231414339762</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-36.94969400495018,175.16284569170142</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>-36.949377911478614,175.1636673262269</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0603/nzd0603.xlsx
+++ b/data/nzd0603/nzd0603.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R366"/>
+  <dimension ref="A1:R370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22386,6 +22386,246 @@
       <c r="R366" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>235.76</v>
+      </c>
+      <c r="C367" t="n">
+        <v>220.42</v>
+      </c>
+      <c r="D367" t="n">
+        <v>229.11</v>
+      </c>
+      <c r="E367" t="n">
+        <v>222.21</v>
+      </c>
+      <c r="F367" t="n">
+        <v>216.38</v>
+      </c>
+      <c r="G367" t="n">
+        <v>222.56</v>
+      </c>
+      <c r="H367" t="n">
+        <v>207.17</v>
+      </c>
+      <c r="I367" t="n">
+        <v>213.34</v>
+      </c>
+      <c r="J367" t="n">
+        <v>223.38</v>
+      </c>
+      <c r="K367" t="n">
+        <v>275.8</v>
+      </c>
+      <c r="L367" t="n">
+        <v>296.33</v>
+      </c>
+      <c r="M367" t="n">
+        <v>235.81</v>
+      </c>
+      <c r="N367" t="n">
+        <v>220.12</v>
+      </c>
+      <c r="O367" t="n">
+        <v>223.69</v>
+      </c>
+      <c r="P367" t="n">
+        <v>247.69</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>232.99</v>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>238.69</v>
+      </c>
+      <c r="C368" t="n">
+        <v>223.47</v>
+      </c>
+      <c r="D368" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="E368" t="n">
+        <v>226.88</v>
+      </c>
+      <c r="F368" t="n">
+        <v>218.04</v>
+      </c>
+      <c r="G368" t="n">
+        <v>226.31</v>
+      </c>
+      <c r="H368" t="n">
+        <v>208.16</v>
+      </c>
+      <c r="I368" t="n">
+        <v>214.37</v>
+      </c>
+      <c r="J368" t="n">
+        <v>225.88</v>
+      </c>
+      <c r="K368" t="n">
+        <v>286.58</v>
+      </c>
+      <c r="L368" t="n">
+        <v>310.51</v>
+      </c>
+      <c r="M368" t="n">
+        <v>236.32</v>
+      </c>
+      <c r="N368" t="n">
+        <v>228.84</v>
+      </c>
+      <c r="O368" t="n">
+        <v>223.04</v>
+      </c>
+      <c r="P368" t="n">
+        <v>260.31</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>235.04</v>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>237.55</v>
+      </c>
+      <c r="C369" t="n">
+        <v>223.45</v>
+      </c>
+      <c r="D369" t="n">
+        <v>231.15</v>
+      </c>
+      <c r="E369" t="n">
+        <v>225.97</v>
+      </c>
+      <c r="F369" t="n">
+        <v>218.12</v>
+      </c>
+      <c r="G369" t="n">
+        <v>227.04</v>
+      </c>
+      <c r="H369" t="n">
+        <v>209.27</v>
+      </c>
+      <c r="I369" t="n">
+        <v>215.11</v>
+      </c>
+      <c r="J369" t="n">
+        <v>226.51</v>
+      </c>
+      <c r="K369" t="n">
+        <v>281.74</v>
+      </c>
+      <c r="L369" t="n">
+        <v>310.51</v>
+      </c>
+      <c r="M369" t="n">
+        <v>237.27</v>
+      </c>
+      <c r="N369" t="n">
+        <v>227.56</v>
+      </c>
+      <c r="O369" t="n">
+        <v>224.11</v>
+      </c>
+      <c r="P369" t="n">
+        <v>256.15</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>234.83</v>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>236.67</v>
+      </c>
+      <c r="C370" t="n">
+        <v>222.62</v>
+      </c>
+      <c r="D370" t="n">
+        <v>230.17</v>
+      </c>
+      <c r="E370" t="n">
+        <v>225.97</v>
+      </c>
+      <c r="F370" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="G370" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="H370" t="n">
+        <v>208.54</v>
+      </c>
+      <c r="I370" t="n">
+        <v>215.28</v>
+      </c>
+      <c r="J370" t="n">
+        <v>224.13</v>
+      </c>
+      <c r="K370" t="n">
+        <v>279.68</v>
+      </c>
+      <c r="L370" t="n">
+        <v>310.19</v>
+      </c>
+      <c r="M370" t="n">
+        <v>235.37</v>
+      </c>
+      <c r="N370" t="n">
+        <v>225.59</v>
+      </c>
+      <c r="O370" t="n">
+        <v>221.39</v>
+      </c>
+      <c r="P370" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>230.86</v>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B376"/>
+  <dimension ref="A1:B380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26163,6 +26403,46 @@
       </c>
       <c r="B376" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>-0.92</v>
       </c>
     </row>
   </sheetData>
@@ -26325,28 +26605,28 @@
         <v>0.0619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06610337059642483</v>
+        <v>0.0757377333076882</v>
       </c>
       <c r="J2" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K2" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0106211595719965</v>
+        <v>0.01405096978733389</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4077251853987</v>
+        <v>3.425091190525591</v>
       </c>
       <c r="N2" t="n">
-        <v>22.39337408101193</v>
+        <v>22.39408646072981</v>
       </c>
       <c r="O2" t="n">
-        <v>4.732163784254717</v>
+        <v>4.732239053633049</v>
       </c>
       <c r="P2" t="n">
-        <v>230.7350450363648</v>
+        <v>230.6337012802456</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26397,28 +26677,28 @@
         <v>0.0871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1654138627581607</v>
+        <v>0.161416603631091</v>
       </c>
       <c r="J3" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K3" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05616356286532642</v>
+        <v>0.05464260611179306</v>
       </c>
       <c r="M3" t="n">
-        <v>3.529210912868224</v>
+        <v>3.50749548575273</v>
       </c>
       <c r="N3" t="n">
-        <v>25.25239613410625</v>
+        <v>25.03297416606557</v>
       </c>
       <c r="O3" t="n">
-        <v>5.025176229159158</v>
+        <v>5.003296330027392</v>
       </c>
       <c r="P3" t="n">
-        <v>220.0722867987749</v>
+        <v>220.1144640509372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26469,28 +26749,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2054688003643537</v>
+        <v>0.2002110261304826</v>
       </c>
       <c r="J4" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K4" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06305565936270641</v>
+        <v>0.06118557091450083</v>
       </c>
       <c r="M4" t="n">
-        <v>3.997846538988547</v>
+        <v>3.985459500821596</v>
       </c>
       <c r="N4" t="n">
-        <v>34.66000570774716</v>
+        <v>34.36241597865288</v>
       </c>
       <c r="O4" t="n">
-        <v>5.887274896566931</v>
+        <v>5.86194643259838</v>
       </c>
       <c r="P4" t="n">
-        <v>227.6957796581765</v>
+        <v>227.7510110540248</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26541,28 +26821,28 @@
         <v>0.1326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4586225393735585</v>
+        <v>0.4603521824565128</v>
       </c>
       <c r="J5" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K5" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2134052353074795</v>
+        <v>0.2182467882679627</v>
       </c>
       <c r="M5" t="n">
-        <v>4.548108116202442</v>
+        <v>4.518814483761749</v>
       </c>
       <c r="N5" t="n">
-        <v>42.83550683264401</v>
+        <v>42.41106657695445</v>
       </c>
       <c r="O5" t="n">
-        <v>6.54488401980081</v>
+        <v>6.512377951021765</v>
       </c>
       <c r="P5" t="n">
-        <v>212.336319132464</v>
+        <v>212.3181181992747</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26613,28 +26893,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3141249204889434</v>
+        <v>0.3196334585536348</v>
       </c>
       <c r="J6" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K6" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1170166812579085</v>
+        <v>0.1228103465011542</v>
       </c>
       <c r="M6" t="n">
-        <v>4.517089670920249</v>
+        <v>4.492517285469455</v>
       </c>
       <c r="N6" t="n">
-        <v>40.96294261139854</v>
+        <v>40.59977171761361</v>
       </c>
       <c r="O6" t="n">
-        <v>6.400229887386744</v>
+        <v>6.371795015348</v>
       </c>
       <c r="P6" t="n">
-        <v>206.6588120420485</v>
+        <v>206.6008572419287</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26685,28 +26965,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4358566083881402</v>
+        <v>0.4417180941130496</v>
       </c>
       <c r="J7" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K7" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2652085356923408</v>
+        <v>0.2739993178707315</v>
       </c>
       <c r="M7" t="n">
-        <v>3.887013283582231</v>
+        <v>3.874216321476332</v>
       </c>
       <c r="N7" t="n">
-        <v>28.95646330123864</v>
+        <v>28.76328643473829</v>
       </c>
       <c r="O7" t="n">
-        <v>5.381121007860596</v>
+        <v>5.363141470699639</v>
       </c>
       <c r="P7" t="n">
-        <v>211.347332222951</v>
+        <v>211.2856403866454</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26757,28 +27037,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1488672904966792</v>
+        <v>0.1365605435575563</v>
       </c>
       <c r="J8" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K8" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04222441098443652</v>
+        <v>0.0360546940654527</v>
       </c>
       <c r="M8" t="n">
-        <v>3.594096454626023</v>
+        <v>3.635631632632353</v>
       </c>
       <c r="N8" t="n">
-        <v>27.71441398646087</v>
+        <v>27.79728625704277</v>
       </c>
       <c r="O8" t="n">
-        <v>5.264448117937992</v>
+        <v>5.272313178960708</v>
       </c>
       <c r="P8" t="n">
-        <v>210.3601350728319</v>
+        <v>210.4894947081515</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26829,28 +27109,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1807173595029905</v>
+        <v>0.1771964921781574</v>
       </c>
       <c r="J9" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K9" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08000954205093358</v>
+        <v>0.07861971015707891</v>
       </c>
       <c r="M9" t="n">
-        <v>3.073846188402372</v>
+        <v>3.060575283303941</v>
       </c>
       <c r="N9" t="n">
-        <v>20.65964832515063</v>
+        <v>20.47284976279697</v>
       </c>
       <c r="O9" t="n">
-        <v>4.545288585464142</v>
+        <v>4.524693333563831</v>
       </c>
       <c r="P9" t="n">
-        <v>211.4809363509155</v>
+        <v>211.517952357803</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26901,28 +27181,28 @@
         <v>0.0697</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.009956237753963742</v>
+        <v>-0.03080898511036912</v>
       </c>
       <c r="J10" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K10" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L10" t="n">
-        <v>4.085550313148723e-05</v>
+        <v>0.0003965282928477531</v>
       </c>
       <c r="M10" t="n">
-        <v>9.229037907255156</v>
+        <v>9.222922809941661</v>
       </c>
       <c r="N10" t="n">
-        <v>133.4762057126491</v>
+        <v>133.1278566291171</v>
       </c>
       <c r="O10" t="n">
-        <v>11.55319028288936</v>
+        <v>11.53810455097011</v>
       </c>
       <c r="P10" t="n">
-        <v>235.387946201502</v>
+        <v>235.6072783618174</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26973,28 +27253,28 @@
         <v>0.0313</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.339156481418856</v>
+        <v>-0.2946043937165951</v>
       </c>
       <c r="J11" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K11" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03158719426556844</v>
+        <v>0.02392151204245496</v>
       </c>
       <c r="M11" t="n">
-        <v>10.34188091408395</v>
+        <v>10.54497490355152</v>
       </c>
       <c r="N11" t="n">
-        <v>194.589733932278</v>
+        <v>197.5939390267484</v>
       </c>
       <c r="O11" t="n">
-        <v>13.94954242734427</v>
+        <v>14.05681112581187</v>
       </c>
       <c r="P11" t="n">
-        <v>268.1948368592135</v>
+        <v>267.726268899373</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27045,28 +27325,28 @@
         <v>0.0382</v>
       </c>
       <c r="I12" t="n">
-        <v>1.055204354024442</v>
+        <v>1.150839886279276</v>
       </c>
       <c r="J12" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K12" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1977198835107682</v>
+        <v>0.2150342124885068</v>
       </c>
       <c r="M12" t="n">
-        <v>11.33454946469856</v>
+        <v>11.83993435624549</v>
       </c>
       <c r="N12" t="n">
-        <v>249.2415456650735</v>
+        <v>269.7190569050006</v>
       </c>
       <c r="O12" t="n">
-        <v>15.78738565010286</v>
+        <v>16.42312567403053</v>
       </c>
       <c r="P12" t="n">
-        <v>232.5454652160234</v>
+        <v>231.5407937187653</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27117,28 +27397,28 @@
         <v>0.1141</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4418766913363186</v>
+        <v>0.4366788299437387</v>
       </c>
       <c r="J13" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K13" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08369310679889574</v>
+        <v>0.08353116866704302</v>
       </c>
       <c r="M13" t="n">
-        <v>6.243207182394217</v>
+        <v>6.203207267083586</v>
       </c>
       <c r="N13" t="n">
-        <v>116.8998044304105</v>
+        <v>115.70123584614</v>
       </c>
       <c r="O13" t="n">
-        <v>10.81202129254334</v>
+        <v>10.75645089451627</v>
       </c>
       <c r="P13" t="n">
-        <v>227.0710406764238</v>
+        <v>227.1259749883684</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27189,28 +27469,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03093109674258512</v>
+        <v>0.04764317028141991</v>
       </c>
       <c r="J14" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K14" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001460020186228261</v>
+        <v>0.003455398855207847</v>
       </c>
       <c r="M14" t="n">
-        <v>4.123631534869624</v>
+        <v>4.167416678832953</v>
       </c>
       <c r="N14" t="n">
-        <v>35.85735258642092</v>
+        <v>36.27774871994248</v>
       </c>
       <c r="O14" t="n">
-        <v>5.988100916519437</v>
+        <v>6.023101254332562</v>
       </c>
       <c r="P14" t="n">
-        <v>216.6232877384011</v>
+        <v>216.4467240430816</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27261,28 +27541,28 @@
         <v>0.1828</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0231715491057289</v>
+        <v>-0.02892044218495123</v>
       </c>
       <c r="J15" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K15" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0005132617466458989</v>
+        <v>0.0008158160031981332</v>
       </c>
       <c r="M15" t="n">
-        <v>5.265117646099612</v>
+        <v>5.233314053186058</v>
       </c>
       <c r="N15" t="n">
-        <v>57.64415067643471</v>
+        <v>57.11162752039407</v>
       </c>
       <c r="O15" t="n">
-        <v>7.592374508441658</v>
+        <v>7.557223532514707</v>
       </c>
       <c r="P15" t="n">
-        <v>226.4669654231213</v>
+        <v>226.527416969376</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27333,28 +27613,28 @@
         <v>0.0747</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9697370413779861</v>
+        <v>0.9760925663010714</v>
       </c>
       <c r="J16" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K16" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1537348054470583</v>
+        <v>0.1581861011755478</v>
       </c>
       <c r="M16" t="n">
-        <v>12.05430471538542</v>
+        <v>11.99013844473164</v>
       </c>
       <c r="N16" t="n">
-        <v>283.6764163853453</v>
+        <v>280.9766613167295</v>
       </c>
       <c r="O16" t="n">
-        <v>16.84269623265068</v>
+        <v>16.76235846522587</v>
       </c>
       <c r="P16" t="n">
-        <v>224.6642448742422</v>
+        <v>224.5971161542599</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27405,28 +27685,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3744141585757032</v>
+        <v>0.3713544133761145</v>
       </c>
       <c r="J17" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K17" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1113970648036677</v>
+        <v>0.1118764627059695</v>
       </c>
       <c r="M17" t="n">
-        <v>5.623592905340803</v>
+        <v>5.57263281791776</v>
       </c>
       <c r="N17" t="n">
-        <v>61.52054354226006</v>
+        <v>60.90772982814921</v>
       </c>
       <c r="O17" t="n">
-        <v>7.843503269729672</v>
+        <v>7.804340447991055</v>
       </c>
       <c r="P17" t="n">
-        <v>225.0548661060871</v>
+        <v>225.0870688869078</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27464,7 +27744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R366"/>
+  <dimension ref="A1:R370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61071,6 +61351,374 @@
         </is>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-36.947489902386494,175.15217445326238</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-36.948104028193825,175.15267527065765</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-36.94850343663014,175.15333303521203</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-36.94893912239727,175.15405296764146</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-36.949366555020625,175.1547791299254</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-36.9496748274151,175.15555131065852</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-36.95008795178062,175.15630731437793</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-36.95032272821679,175.1571592931436</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-36.95039680228301,175.15798046706536</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-36.94998439555573,175.1589231968369</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-36.9498583840329,175.15983699304573</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-36.950460270501544,175.16067726840637</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-36.95041737949142,175.16144896610442</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-36.95019156884519,175.1623028151719</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>-36.949657724790335,175.16281356160084</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-36.94934803731493,175.163640825769</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>-36.94747154089194,175.15219808764087</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>-36.94808491458825,175.15269987305635</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>-36.948483275720555,175.15334876469524</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-36.948903473327476,175.154080820811</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-36.949353884149744,175.15478903257784</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-36.949643807935615,175.155568003173</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-36.950079762956115,175.15631172213327</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-36.95031420850068,175.1571638789062</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-36.95037435001173,175.15798273620712</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-36.94988758112858,175.1589329772402</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-36.949731034391085,175.15984985663528</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-36.950455690224,175.16067773101202</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>-36.95034173834773,175.16142248374607</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>-36.950197207216995,175.16230478925877</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>-36.94956504142208,175.16273148039124</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>-36.949332990129186,175.16362747788042</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>-36.94747868495518,175.15218889201373</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>-36.94808503992338,175.1526997117292</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>-36.94848785774562,175.15334518981342</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-36.948910419934684,175.15407539332173</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-36.94935327350533,175.15478950981404</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-36.9496377694767,175.15557125264763</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-36.95007058154666,175.15631666416095</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-36.9503080875395,175.15716717353118</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-36.95036869203936,175.15798330803068</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-36.94993104883075,175.15892858604101</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-36.949731034391085,175.15984985663528</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>-36.950447158334434,175.16067859272835</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-36.950352841635414,175.1614263710612</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-36.95018792558954,175.16230153960825</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-36.949595593157575,175.16275853724946</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>-36.94933453154831,175.16362884522488</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>-36.94748419967023,175.1521817936337</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>-36.94809024133127,175.1526930166514</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>-36.948495341719706,175.15333935083885</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-36.948910419934684,175.15407539332173</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>-36.94935480011634,175.15478831672354</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>-36.94963975472348,175.15557018432727</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>-36.950076619770925,175.15631341399873</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>-36.95030668137272,175.15716793040443</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>-36.95039006660163,175.157981147808</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>-36.949949549546865,175.15892671705842</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>-36.949733908289936,175.1598495663431</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>-36.95046422211355,175.16067686929557</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>-36.95036993028874,175.16143235388455</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>-36.95021152000677,175.16230980040373</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>-36.94964810393658,175.16280504127573</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>-36.9493636717061,175.16365469455639</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0603/nzd0603.xlsx
+++ b/data/nzd0603/nzd0603.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R370"/>
+  <dimension ref="A1:R372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22624,6 +22624,126 @@
         <v>230.86</v>
       </c>
       <c r="R370" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>236.31</v>
+      </c>
+      <c r="C371" t="n">
+        <v>222.32</v>
+      </c>
+      <c r="D371" t="n">
+        <v>230</v>
+      </c>
+      <c r="E371" t="n">
+        <v>226.22</v>
+      </c>
+      <c r="F371" t="n">
+        <v>218.63</v>
+      </c>
+      <c r="G371" t="n">
+        <v>225</v>
+      </c>
+      <c r="H371" t="n">
+        <v>209.68</v>
+      </c>
+      <c r="I371" t="n">
+        <v>214.68</v>
+      </c>
+      <c r="J371" t="n">
+        <v>222.29</v>
+      </c>
+      <c r="K371" t="n">
+        <v>279.68</v>
+      </c>
+      <c r="L371" t="n">
+        <v>310.19</v>
+      </c>
+      <c r="M371" t="n">
+        <v>233.89</v>
+      </c>
+      <c r="N371" t="n">
+        <v>222.19</v>
+      </c>
+      <c r="O371" t="n">
+        <v>218.84</v>
+      </c>
+      <c r="P371" t="n">
+        <v>243.35</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>228.87</v>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>237.07</v>
+      </c>
+      <c r="C372" t="n">
+        <v>223.77</v>
+      </c>
+      <c r="D372" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="E372" t="n">
+        <v>225.94</v>
+      </c>
+      <c r="F372" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="G372" t="n">
+        <v>225.83</v>
+      </c>
+      <c r="H372" t="n">
+        <v>211.81</v>
+      </c>
+      <c r="I372" t="n">
+        <v>216.12</v>
+      </c>
+      <c r="J372" t="n">
+        <v>220.24</v>
+      </c>
+      <c r="K372" t="n">
+        <v>285.97</v>
+      </c>
+      <c r="L372" t="n">
+        <v>318.32</v>
+      </c>
+      <c r="M372" t="n">
+        <v>233.63</v>
+      </c>
+      <c r="N372" t="n">
+        <v>221.67</v>
+      </c>
+      <c r="O372" t="n">
+        <v>216.28</v>
+      </c>
+      <c r="P372" t="n">
+        <v>244.84</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>226.5</v>
+      </c>
+      <c r="R372" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22640,7 +22760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B380"/>
+  <dimension ref="A1:B382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26443,6 +26563,26 @@
       </c>
       <c r="B380" t="n">
         <v>-0.92</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>-0.97</v>
       </c>
     </row>
   </sheetData>
@@ -26605,28 +26745,28 @@
         <v>0.0619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0757377333076882</v>
+        <v>0.07987034682192654</v>
       </c>
       <c r="J2" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K2" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01405096978733389</v>
+        <v>0.01570909208961968</v>
       </c>
       <c r="M2" t="n">
-        <v>3.425091190525591</v>
+        <v>3.429704601556507</v>
       </c>
       <c r="N2" t="n">
-        <v>22.39408646072981</v>
+        <v>22.3611954568896</v>
       </c>
       <c r="O2" t="n">
-        <v>4.732239053633049</v>
+        <v>4.728762571422846</v>
       </c>
       <c r="P2" t="n">
-        <v>230.6337012802456</v>
+        <v>230.5900260112063</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26677,28 +26817,28 @@
         <v>0.0871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.161416603631091</v>
+        <v>0.1600472929700865</v>
       </c>
       <c r="J3" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K3" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05464260611179306</v>
+        <v>0.05430104929347623</v>
       </c>
       <c r="M3" t="n">
-        <v>3.50749548575273</v>
+        <v>3.49420341134748</v>
       </c>
       <c r="N3" t="n">
-        <v>25.03297416606557</v>
+        <v>24.90931605275887</v>
       </c>
       <c r="O3" t="n">
-        <v>5.003296330027392</v>
+        <v>4.99092336674877</v>
       </c>
       <c r="P3" t="n">
-        <v>220.1144640509372</v>
+        <v>220.1289781755426</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26749,28 +26889,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2002110261304826</v>
+        <v>0.1976663611180972</v>
       </c>
       <c r="J4" t="n">
+        <v>371</v>
+      </c>
+      <c r="K4" t="n">
         <v>369</v>
       </c>
-      <c r="K4" t="n">
-        <v>367</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06118557091450083</v>
+        <v>0.06028885848127219</v>
       </c>
       <c r="M4" t="n">
-        <v>3.985459500821596</v>
+        <v>3.978886722864091</v>
       </c>
       <c r="N4" t="n">
-        <v>34.36241597865288</v>
+        <v>34.21105578132853</v>
       </c>
       <c r="O4" t="n">
-        <v>5.86194643259838</v>
+        <v>5.849021779864435</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7510110540248</v>
+        <v>227.7778647456925</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26821,28 +26961,28 @@
         <v>0.1326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4603521824565128</v>
+        <v>0.4619748731095388</v>
       </c>
       <c r="J5" t="n">
+        <v>371</v>
+      </c>
+      <c r="K5" t="n">
         <v>369</v>
       </c>
-      <c r="K5" t="n">
-        <v>367</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2182467882679627</v>
+        <v>0.2212641783606535</v>
       </c>
       <c r="M5" t="n">
-        <v>4.518814483761749</v>
+        <v>4.50204046704602</v>
       </c>
       <c r="N5" t="n">
-        <v>42.41106657695445</v>
+        <v>42.19484348455831</v>
       </c>
       <c r="O5" t="n">
-        <v>6.512377951021765</v>
+        <v>6.495755805490098</v>
       </c>
       <c r="P5" t="n">
-        <v>212.3181181992747</v>
+        <v>212.3009918423641</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26893,28 +27033,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3196334585536348</v>
+        <v>0.3233674759152104</v>
       </c>
       <c r="J6" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K6" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1228103465011542</v>
+        <v>0.126341369389697</v>
       </c>
       <c r="M6" t="n">
-        <v>4.492517285469455</v>
+        <v>4.484798284788698</v>
       </c>
       <c r="N6" t="n">
-        <v>40.59977171761361</v>
+        <v>40.45203315343155</v>
       </c>
       <c r="O6" t="n">
-        <v>6.371795015348</v>
+        <v>6.360191282770633</v>
       </c>
       <c r="P6" t="n">
-        <v>206.6008572419287</v>
+        <v>206.5613974665215</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26965,28 +27105,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4417180941130496</v>
+        <v>0.4442161359952628</v>
       </c>
       <c r="J7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2739993178707315</v>
+        <v>0.2782060048331182</v>
       </c>
       <c r="M7" t="n">
-        <v>3.874216321476332</v>
+        <v>3.865292289278262</v>
       </c>
       <c r="N7" t="n">
-        <v>28.76328643473829</v>
+        <v>28.64091672968623</v>
       </c>
       <c r="O7" t="n">
-        <v>5.363141470699639</v>
+        <v>5.351720912910746</v>
       </c>
       <c r="P7" t="n">
-        <v>211.2856403866454</v>
+        <v>211.2592380120729</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27037,28 +27177,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1365605435575563</v>
+        <v>0.1331420284962241</v>
       </c>
       <c r="J8" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K8" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0360546940654527</v>
+        <v>0.03461680842303039</v>
       </c>
       <c r="M8" t="n">
-        <v>3.635631632632353</v>
+        <v>3.638420079861772</v>
       </c>
       <c r="N8" t="n">
-        <v>27.79728625704277</v>
+        <v>27.7129768064861</v>
       </c>
       <c r="O8" t="n">
-        <v>5.272313178960708</v>
+        <v>5.264311617532353</v>
       </c>
       <c r="P8" t="n">
-        <v>210.4894947081515</v>
+        <v>210.5255876356434</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27109,28 +27249,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1771964921781574</v>
+        <v>0.1763801800914934</v>
       </c>
       <c r="J9" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K9" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07861971015707891</v>
+        <v>0.07871912337225273</v>
       </c>
       <c r="M9" t="n">
-        <v>3.060575283303941</v>
+        <v>3.04865804084557</v>
       </c>
       <c r="N9" t="n">
-        <v>20.47284976279697</v>
+        <v>20.36867881904649</v>
       </c>
       <c r="O9" t="n">
-        <v>4.524693333563831</v>
+        <v>4.513167271334677</v>
       </c>
       <c r="P9" t="n">
-        <v>211.517952357803</v>
+        <v>211.526570648961</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27181,28 +27321,28 @@
         <v>0.0697</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03080898511036912</v>
+        <v>-0.04460694375659439</v>
       </c>
       <c r="J10" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K10" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0003965282928477531</v>
+        <v>0.0008338400353397057</v>
       </c>
       <c r="M10" t="n">
-        <v>9.222922809941661</v>
+        <v>9.235191550580536</v>
       </c>
       <c r="N10" t="n">
-        <v>133.1278566291171</v>
+        <v>133.3863535461619</v>
       </c>
       <c r="O10" t="n">
-        <v>11.53810455097011</v>
+        <v>11.5493009981627</v>
       </c>
       <c r="P10" t="n">
-        <v>235.6072783618174</v>
+        <v>235.7530984967386</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27253,28 +27393,28 @@
         <v>0.0313</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2946043937165951</v>
+        <v>-0.2712596245757051</v>
       </c>
       <c r="J11" t="n">
+        <v>371</v>
+      </c>
+      <c r="K11" t="n">
         <v>369</v>
       </c>
-      <c r="K11" t="n">
-        <v>367</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.02392151204245496</v>
+        <v>0.02028510892961499</v>
       </c>
       <c r="M11" t="n">
-        <v>10.54497490355152</v>
+        <v>10.6544253003222</v>
       </c>
       <c r="N11" t="n">
-        <v>197.5939390267484</v>
+        <v>199.3691658153287</v>
       </c>
       <c r="O11" t="n">
-        <v>14.05681112581187</v>
+        <v>14.11981465230081</v>
       </c>
       <c r="P11" t="n">
-        <v>267.726268899373</v>
+        <v>267.4795692016289</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27325,28 +27465,28 @@
         <v>0.0382</v>
       </c>
       <c r="I12" t="n">
-        <v>1.150839886279276</v>
+        <v>1.204177661445423</v>
       </c>
       <c r="J12" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K12" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2150342124885068</v>
+        <v>0.223320156434984</v>
       </c>
       <c r="M12" t="n">
-        <v>11.83993435624549</v>
+        <v>12.13385018349089</v>
       </c>
       <c r="N12" t="n">
-        <v>269.7190569050006</v>
+        <v>282.8907468674263</v>
       </c>
       <c r="O12" t="n">
-        <v>16.42312567403053</v>
+        <v>16.81935631549038</v>
       </c>
       <c r="P12" t="n">
-        <v>231.5407937187653</v>
+        <v>230.9778746031597</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27397,28 +27537,28 @@
         <v>0.1141</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4366788299437387</v>
+        <v>0.4316399881143139</v>
       </c>
       <c r="J13" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K13" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08353116866704302</v>
+        <v>0.08251125633245904</v>
       </c>
       <c r="M13" t="n">
-        <v>6.203207267083586</v>
+        <v>6.196882360127686</v>
       </c>
       <c r="N13" t="n">
-        <v>115.70123584614</v>
+        <v>115.2043699068205</v>
       </c>
       <c r="O13" t="n">
-        <v>10.75645089451627</v>
+        <v>10.73332986108321</v>
       </c>
       <c r="P13" t="n">
-        <v>227.1259749883684</v>
+        <v>227.179475487179</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27469,28 +27609,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04764317028141991</v>
+        <v>0.05197165639645696</v>
       </c>
       <c r="J14" t="n">
+        <v>371</v>
+      </c>
+      <c r="K14" t="n">
         <v>369</v>
       </c>
-      <c r="K14" t="n">
-        <v>367</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.003455398855207847</v>
+        <v>0.004143084586622048</v>
       </c>
       <c r="M14" t="n">
-        <v>4.167416678832953</v>
+        <v>4.168790266321782</v>
       </c>
       <c r="N14" t="n">
-        <v>36.27774871994248</v>
+        <v>36.17661981770221</v>
       </c>
       <c r="O14" t="n">
-        <v>6.023101254332562</v>
+        <v>6.01470030988263</v>
       </c>
       <c r="P14" t="n">
-        <v>216.4467240430816</v>
+        <v>216.4007949027748</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27541,28 +27681,28 @@
         <v>0.1828</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02892044218495123</v>
+        <v>-0.03728803603249795</v>
       </c>
       <c r="J15" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K15" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0008158160031981332</v>
+        <v>0.001361510791241471</v>
       </c>
       <c r="M15" t="n">
-        <v>5.233314053186058</v>
+        <v>5.242353526348946</v>
       </c>
       <c r="N15" t="n">
-        <v>57.11162752039407</v>
+        <v>57.16975919378786</v>
       </c>
       <c r="O15" t="n">
-        <v>7.557223532514707</v>
+        <v>7.56106865421733</v>
       </c>
       <c r="P15" t="n">
-        <v>226.527416969376</v>
+        <v>226.6158060210159</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27613,28 +27753,28 @@
         <v>0.0747</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9760925663010714</v>
+        <v>0.969629544624345</v>
       </c>
       <c r="J16" t="n">
+        <v>371</v>
+      </c>
+      <c r="K16" t="n">
         <v>369</v>
       </c>
-      <c r="K16" t="n">
-        <v>367</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.1581861011755478</v>
+        <v>0.1577687118458746</v>
       </c>
       <c r="M16" t="n">
-        <v>11.99013844473164</v>
+        <v>11.94533108842872</v>
       </c>
       <c r="N16" t="n">
-        <v>280.9766613167295</v>
+        <v>279.6687213513966</v>
       </c>
       <c r="O16" t="n">
-        <v>16.76235846522587</v>
+        <v>16.72329875806196</v>
       </c>
       <c r="P16" t="n">
-        <v>224.5971161542599</v>
+        <v>224.6656908925286</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27685,28 +27825,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3713544133761145</v>
+        <v>0.3639865019289594</v>
       </c>
       <c r="J17" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K17" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1118764627059695</v>
+        <v>0.1085569003953933</v>
       </c>
       <c r="M17" t="n">
-        <v>5.57263281791776</v>
+        <v>5.565025621838904</v>
       </c>
       <c r="N17" t="n">
-        <v>60.90772982814921</v>
+        <v>60.86368448888131</v>
       </c>
       <c r="O17" t="n">
-        <v>7.804340447991055</v>
+        <v>7.801518088736404</v>
       </c>
       <c r="P17" t="n">
-        <v>225.0870688869078</v>
+        <v>225.1649419610919</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27744,7 +27884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R370"/>
+  <dimension ref="A1:R372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61719,6 +61859,190 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>-36.947486455689905,175.15217888975067</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>-36.94809212135813,175.15269059674355</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>-36.948496639960084,175.1533383379554</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-36.94890851152614,175.15407688439032</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>-36.94934938064727,175.1547925521945</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>-36.949654644074016,175.15556217192278</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>-36.9500671902152,175.1563184895943</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>-36.95031164431424,175.15716525908704</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>-36.950406591473275,175.15797947771924</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>-36.949949549546865,175.15892671705842</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>-36.949733908289936,175.1598495663431</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>-36.95047751389936,175.16067552683174</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>-36.95039942339501,175.16144267957623</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>-36.9502336397722,175.1623175449044</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>-36.94968959845355,175.1628417892584</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>-36.94937827848305,175.1636676517855</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-36.947481692981626,175.1521850201702</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-36.948083034561215,175.1527022929638</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-36.948488239581046,175.15334489190658</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-36.94891064894371,175.15407521439352</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-36.94934808302788,175.15479356632127</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-36.9496477784291,175.15556586653187</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-36.95004957183424,175.15632797294066</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>-36.950299733254504,175.15717167024823</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>-36.95042500233563,175.15797761702188</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>-36.94989305949602,175.15893242380417</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>-36.94966089329672,175.15985694157456</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>-36.95047984894281,175.16067529099348</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>-36.95040393410526,175.1614442588004</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>-36.95025584628105,175.16232531978048</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>-36.94967865565299,175.16283209819358</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>-36.949395674491676,175.1636830832659</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
